--- a/data/fmsForecastOutput/File1/RPT_RPT9073295656307CV_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT9073295656307CV_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>174.6105636000918</v>
+        <v>67.57698478948238</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>193.8349148664806</v>
+        <v>76.82778635685057</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>212.4791371273343</v>
+        <v>86.14293662094818</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>231.0605279934124</v>
+        <v>95.70578914194253</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>250.3323613677185</v>
+        <v>105.8258076667197</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>15.04994714431628</v>
+        <v>5.824561975432742</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>17.66559769565828</v>
+        <v>7.001879751968284</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>20.43798824678218</v>
+        <v>8.285935033457696</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>23.70543711770954</v>
+        <v>9.81884524374397</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>27.67382535668783</v>
+        <v>11.69886667308405</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>18006497.46848061</v>
+        <v>6968792.611690119</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>21464012.74399903</v>
+        <v>8507407.381134508</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>25173599.79554611</v>
+        <v>10205838.75210906</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>29564351.49446153</v>
+        <v>12245620.72466085</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>35054009.07985747</v>
+        <v>14818774.53863548</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>177.557043089881</v>
+        <v>68.71731785730319</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>197.1057971618221</v>
+        <v>78.12422279276308</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>216.0646327963575</v>
+        <v>87.59656228202309</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>234.9595767828759</v>
+        <v>97.32078389911361</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>254.5566142032447</v>
+        <v>107.6115734609045</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>18.32704930592181</v>
+        <v>7.092851123365375</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>21.48927828423002</v>
+        <v>8.517421549781028</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>24.83465975483346</v>
+        <v>10.06842624733258</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>28.76526311143534</v>
+        <v>11.91463652343951</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>33.52324769428306</v>
+        <v>14.17165860409003</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>18006497.46848061</v>
+        <v>6968792.611690119</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>21464012.74399903</v>
+        <v>8507407.381134508</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>25173599.79554611</v>
+        <v>10205838.75210906</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>29564351.49446153</v>
+        <v>12245620.72466085</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>35054009.07985747</v>
+        <v>14818774.53863548</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>519.2270500993797</v>
+        <v>200.9392608743729</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>578.8843298642934</v>
+        <v>229.4358624462139</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>637.5791984170925</v>
+        <v>258.4780534123348</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>691.3851736741429</v>
+        <v>286.3725571431361</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>745.3803389396002</v>
+        <v>315.1024756450204</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>33.915557512716</v>
+        <v>13.12521575569505</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>38.45886485221644</v>
+        <v>15.24284277679311</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>43.84151265653367</v>
+        <v>17.77358621210825</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>50.56209796827774</v>
+        <v>20.94288081526297</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>58.77876784619508</v>
+        <v>24.84816716530112</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>8994896.528709207</v>
+        <v>3480997.108633594</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>10258567.536894</v>
+        <v>4065895.670110427</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>11754657.1260822</v>
+        <v>4765401.537600892</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>13612808.28135085</v>
+        <v>5638441.299967806</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>15925073.75878601</v>
+        <v>6732174.03797076</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>527.3907381151084</v>
+        <v>204.098582861884</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>587.9859956293992</v>
+        <v>233.0432299750668</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>647.6037101604607</v>
+        <v>262.5420446596462</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>702.255664445947</v>
+        <v>290.8751272853034</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>757.0997833310211</v>
+        <v>320.0567597171954</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>34.05950536336701</v>
+        <v>13.180923128238</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>38.62261740826182</v>
+        <v>15.30774470449402</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>44.02942217099822</v>
+        <v>17.84976574499928</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>50.78149529837508</v>
+        <v>21.03375544903109</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>59.03790614931627</v>
+        <v>24.95771542755352</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>8994896.528709207</v>
+        <v>3480997.108633594</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>10258567.536894</v>
+        <v>4065895.670110427</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>11754657.1260822</v>
+        <v>4765401.537600892</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>13612808.28135085</v>
+        <v>5638441.299967806</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>15925073.75878601</v>
+        <v>6732174.03797076</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>224.1758399761072</v>
+        <v>86.75812768670627</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>246.9553042422038</v>
+        <v>97.88118913579784</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>269.7225371858659</v>
+        <v>109.349350670131</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>292.4492039115007</v>
+        <v>121.1330186830971</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>315.8655032284616</v>
+        <v>133.5292994333823</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>18.47305525339577</v>
+        <v>7.149243587571728</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>21.40873225559567</v>
+        <v>8.485390413045844</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>24.62173680278134</v>
+        <v>9.982002096842551</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>28.47375671640061</v>
+        <v>11.79388440171466</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>33.15460312735435</v>
+        <v>14.01581015760806</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>27001393.99718982</v>
+        <v>10449789.72032371</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>31722580.28089303</v>
+        <v>12573303.05124493</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>36928256.9216283</v>
+        <v>14971240.28970995</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>43177159.77581238</v>
+        <v>17884062.02462866</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>50979082.83864348</v>
+        <v>21550948.57660624</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>227.9215392581805</v>
+        <v>88.20774802324547</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>251.0832910771573</v>
+        <v>99.51732431168331</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>274.232115845487</v>
+        <v>111.17759796222</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>297.3391950565134</v>
+        <v>123.1584623526524</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>321.1473917776399</v>
+        <v>135.762170292809</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>21.65997950203959</v>
+        <v>8.38261280756069</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>25.08835120954721</v>
+        <v>9.943814154477865</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>28.8362187424382</v>
+        <v>11.69061298387013</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>33.31967040121931</v>
+        <v>13.80107110309291</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>38.75540130261877</v>
+        <v>16.38349719201618</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>27001393.99718982</v>
+        <v>10449789.72032371</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>31722580.28089303</v>
+        <v>12573303.05124493</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>36928256.9216283</v>
+        <v>14971240.28970995</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>43177159.77581238</v>
+        <v>17884062.02462866</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>50979082.83864348</v>
+        <v>21550948.57660624</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2282,7 +2282,7 @@
         <v>0.9490429845289819</v>
       </c>
       <c r="AU10" s="154" t="n">
-        <v>0.93</v>
+        <v>0.9424528226375311</v>
       </c>
       <c r="AV10" s="154" t="n">
         <v>0.926953522955747</v>
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>506.0375672472365</v>
+        <v>195.8351438583047</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>565.5537393379285</v>
+        <v>224.1526512082774</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>627.589263725873</v>
+        <v>254.4284207442138</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>691.7922811550793</v>
+        <v>286.5416049610097</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>762.0600458380181</v>
+        <v>322.1541679277299</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>54.19166645380759</v>
+        <v>20.97202556251644</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>62.93353367487809</v>
+        <v>24.94319715690239</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>72.79058061566714</v>
+        <v>29.50973437810113</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>84.72774772866653</v>
+        <v>35.09438523709293</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>98.99946488098674</v>
+        <v>41.85115124222629</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>3429070.50985524</v>
+        <v>1327040.836613773</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>4034074.260010073</v>
+        <v>1598872.711213785</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>4723070.414920569</v>
+        <v>1914760.84150612</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>5560996.508111604</v>
+        <v>2303374.738377089</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>6590314.123265038</v>
+        <v>2785997.21158206</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>666.2156753735758</v>
+        <v>257.8236302438361</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>744.5707409880584</v>
+        <v>295.1045921824605</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>826.2426196236542</v>
+        <v>334.9636729194129</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>910.7680765977258</v>
+        <v>377.2417726023483</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1003.277979686331</v>
+        <v>424.1269234770574</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>62.30083787335663</v>
+        <v>24.11025255257537</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>72.39386599084116</v>
+        <v>28.69272336888875</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>83.78867261781728</v>
+        <v>33.9684262981861</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>97.61953137789919</v>
+        <v>40.43418517168217</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>114.1835531252608</v>
+        <v>48.27009072185239</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>3429070.50985524</v>
+        <v>1327040.836613773</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>4034074.260010073</v>
+        <v>1598872.711213785</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>4723070.414920569</v>
+        <v>1914760.84150612</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>5560996.508111604</v>
+        <v>2303374.738377089</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>6590314.123265038</v>
+        <v>2785997.21158206</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>239.1886412242937</v>
+        <v>92.56789682557992</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>263.7160497436282</v>
+        <v>104.5240461204962</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>288.3687017112615</v>
+        <v>116.9085005132788</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>313.0694917124548</v>
+        <v>129.6739771926123</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>338.5580165193712</v>
+        <v>143.1223623836157</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>19.95518288565184</v>
+        <v>7.722813679778463</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>23.13059813332151</v>
+        <v>9.167829217949889</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>26.6192140522289</v>
+        <v>10.79178281561251</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>30.80758476925652</v>
+        <v>12.76056003693032</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>35.88697857112484</v>
+        <v>15.1708980478851</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>30430464.50704505</v>
+        <v>11776830.55693748</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>35756654.5409031</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>41651327.33654888</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>48738156.28392398</v>
+        <v>20187436.76300574</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>57569396.96190853</v>
+        <v>24336945.7881883</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>246.1712496637491</v>
+        <v>95.27022154421415</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>271.375422630083</v>
+        <v>107.5598440767304</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>296.7106763638</v>
+        <v>120.2904477986835</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>322.0917199878459</v>
+        <v>133.4110012546189</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>348.2527555958733</v>
+        <v>147.2207263024105</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>23.37849463704714</v>
+        <v>9.047662415834457</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>27.08511998648548</v>
+        <v>10.73520680064329</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>31.15307030273366</v>
+        <v>12.62986833822236</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>36.02729531166513</v>
+        <v>14.92257404259399</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>41.92589339526445</v>
+        <v>17.72379508086629</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>30430464.50704505</v>
+        <v>11776830.55693748</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>35756654.5409031</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>41651327.33654888</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>48738156.28392398</v>
+        <v>20187436.76300574</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>57569396.96190853</v>
+        <v>24336945.7881883</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>239.1886412242937</v>
+        <v>92.56789682557994</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>263.7160497436282</v>
+        <v>104.5240461204962</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>288.3687017112615</v>
+        <v>116.9085005132788</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>313.0694917124548</v>
+        <v>129.6739771926123</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>338.5580165193711</v>
+        <v>143.1223623836157</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>19.95518288565184</v>
+        <v>7.722813679778464</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>23.13059813332151</v>
+        <v>9.167829217949889</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>26.6192140522289</v>
+        <v>10.79178281561251</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>30.80758476925652</v>
+        <v>12.76056003693032</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>35.88697857112483</v>
+        <v>15.1708980478851</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>30430464.50704506</v>
+        <v>11776830.55693749</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>35756654.5409031</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>41651327.33654888</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>48738156.28392398</v>
+        <v>20187436.76300574</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>57569396.96190851</v>
+        <v>24336945.7881883</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>246.1712496637492</v>
+        <v>95.27022154421415</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>271.3754226300829</v>
+        <v>107.5598440767304</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>296.7106763638</v>
+        <v>120.2904477986835</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>322.0917199878459</v>
+        <v>133.4110012546188</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>348.2527555958732</v>
+        <v>147.2207263024105</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>23.37849463704715</v>
+        <v>9.047662415834457</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>27.08511998648548</v>
+        <v>10.73520680064329</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>31.15307030273365</v>
+        <v>12.62986833822236</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>36.02729531166514</v>
+        <v>14.92257404259399</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>41.92589339526444</v>
+        <v>17.72379508086628</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>30430464.50704506</v>
+        <v>11776830.55693749</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>35756654.5409031</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>41651327.33654888</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>48738156.28392398</v>
+        <v>20187436.76300574</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>57569396.96190851</v>
+        <v>24336945.7881883</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="AW16" s="176" t="n">
-        <v>0.004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" thickBot="1">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="AW17" s="177" t="n">
-        <v>0.006</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18" ht="30.3" customHeight="1" thickBot="1">
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.646</v>
+        <v>0.25</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.656</v>
+        <v>0.26</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.666</v>
+        <v>0.27</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.6759999999999999</v>
+        <v>0.2799999999999999</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.6859999999999999</v>
+        <v>0.2899999999999999</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.696</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.706</v>
+        <v>0.3099999999999999</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.716</v>
+        <v>0.32</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.726</v>
+        <v>0.33</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.736</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.834</v>
+        <v>0.24</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.844</v>
+        <v>0.25</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.854</v>
+        <v>0.26</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.864</v>
+        <v>0.27</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.874</v>
+        <v>0.28</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.884</v>
+        <v>0.29</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.894</v>
+        <v>0.3</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.904</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.914</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.9239999999999999</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -4417,7 +4417,7 @@
         <v>638.0531763714454</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>683.5994754926789</v>
+        <v>683.5994754926787</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>729.8190325574336</v>
@@ -4432,7 +4432,7 @@
         <v>61.37319407357498</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>70.13324396304046</v>
+        <v>70.13324396304043</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>80.68027776606019</v>
@@ -4447,7 +4447,7 @@
         <v>75593752.53216548</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>87467017.19417563</v>
+        <v>87467017.1941756</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>102196467.3450331</v>
@@ -4467,7 +4467,7 @@
         <v>648.8200541525581</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>695.134927828673</v>
+        <v>695.1349278286727</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>742.1344203916622</v>
@@ -4482,7 +4482,7 @@
         <v>74.57595016107166</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>85.10289033852952</v>
+        <v>85.10289033852949</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>97.7336851965631</v>
@@ -4497,7 +4497,7 @@
         <v>75593752.53216548</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>87467017.19417563</v>
+        <v>87467017.1941756</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>102196467.3450331</v>
@@ -4513,7 +4513,7 @@
         <v>1607.514086994983</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1764.89124958626</v>
+        <v>1764.891249586261</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1914.652247498776</v>
@@ -4528,7 +4528,7 @@
         <v>105.0017260455604</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>117.2526367445623</v>
+        <v>117.2526367445624</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>131.6561941637648</v>
@@ -4543,7 +4543,7 @@
         <v>27847976.86906875</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>31276120.53931096</v>
+        <v>31276120.53931097</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>35299270.64889549</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1632.788662895073</v>
+        <v>1632.788662895072</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>1792.640230577437</v>
@@ -4578,7 +4578,7 @@
         <v>105.447385025904</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>117.7518823422616</v>
+        <v>117.7518823422617</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>132.2204869999946</v>
@@ -4593,7 +4593,7 @@
         <v>27847976.86906875</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>31276120.53931096</v>
+        <v>31276120.53931097</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>35299270.64889549</v>
@@ -4615,13 +4615,13 @@
         <v>694.0250915277945</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>752.8940651847131</v>
+        <v>752.8940651847132</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>809.958282950766</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>865.2243178712512</v>
+        <v>865.2243178712509</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>920.8794661320745</v>
@@ -4636,7 +4636,7 @@
         <v>73.93738718357088</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>84.240908857577</v>
+        <v>84.24090885757697</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>96.65947346474206</v>
@@ -4645,7 +4645,7 @@
         <v>83593508.30256724</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>96712814.08236432</v>
+        <v>96712814.08236434</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>110893023.181061</v>
@@ -4665,13 +4665,13 @@
         <v>705.6213870400744</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>765.4790825372822</v>
+        <v>765.4790825372824</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>823.5002384213285</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>879.691579864963</v>
+        <v>879.6915798649628</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>936.2783705949605</v>
@@ -4680,13 +4680,13 @@
         <v>67.05704440761932</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>76.48700151996886</v>
+        <v>76.48700151996887</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>86.59318744033327</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>98.57776567350123</v>
+        <v>98.5777656735012</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>112.9881322794418</v>
@@ -4695,7 +4695,7 @@
         <v>83593508.30256724</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>96712814.08236432</v>
+        <v>96712814.08236434</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>110893023.181061</v>
@@ -4735,7 +4735,7 @@
         <v>191.8685097413256</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>218.5874729588962</v>
+        <v>218.5874729588961</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>250.6700069020689</v>
@@ -4744,13 +4744,13 @@
         <v>288.6233076017104</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>10616235.42155412</v>
+        <v>10616235.42155413</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>12298877.42284754</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>14183209.11678787</v>
+        <v>14183209.11678786</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>16452402.78940029</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>2062.571309329576</v>
+        <v>2062.571309329577</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>2270.008851058689</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>2481.176613057543</v>
+        <v>2481.176613057542</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>2694.539229085312</v>
@@ -4785,7 +4785,7 @@
         <v>220.7106826995256</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>251.614344262654</v>
+        <v>251.6143442626539</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>288.8108000066136</v>
@@ -4794,13 +4794,13 @@
         <v>332.8910395257876</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>10616235.42155412</v>
+        <v>10616235.42155413</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>12298877.42284754</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>14183209.11678787</v>
+        <v>14183209.11678786</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>16452402.78940029</v>
@@ -4819,13 +4819,13 @@
         <v>740.5046540201389</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>803.9939146639028</v>
+        <v>803.993914663903</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>865.9524924915713</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>926.2300002366524</v>
+        <v>926.2300002366521</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>987.0370608328329</v>
@@ -4834,13 +4834,13 @@
         <v>61.77929571827581</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>70.51849957484833</v>
+        <v>70.51849957484835</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>79.93577187781915</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>91.14560825469265</v>
+        <v>91.14560825469262</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>104.6254293877788</v>
@@ -4869,13 +4869,13 @@
         <v>762.1221272419064</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>827.3451259263115</v>
+        <v>827.3451259263117</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>891.0029008743101</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>952.9226634276282</v>
+        <v>952.9226634276281</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>1015.301246870987</v>
@@ -5023,13 +5023,13 @@
         <v>740.5046540201389</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>803.9939146639028</v>
+        <v>803.993914663903</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>865.9524924915713</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>926.2300002366524</v>
+        <v>926.2300002366521</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>987.0370608328329</v>
@@ -5038,13 +5038,13 @@
         <v>61.77929571827581</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>70.51849957484833</v>
+        <v>70.51849957484835</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>79.93577187781915</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>91.14560825469265</v>
+        <v>91.14560825469262</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>104.6254293877788</v>
@@ -5073,13 +5073,13 @@
         <v>762.1221272419064</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>827.3451259263115</v>
+        <v>827.3451259263117</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>891.0029008743101</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>952.9226634276282</v>
+        <v>952.9226634276281</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1015.301246870987</v>
@@ -5713,7 +5713,7 @@
         <v>1483.644525484691</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>1639.702627229064</v>
+        <v>1639.702627229063</v>
       </c>
       <c r="P49" s="159" t="n">
         <v>1821.392186934197</v>
@@ -5739,7 +5739,7 @@
         <v>0.2983037044537724</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.309680728496895</v>
+        <v>0.3096807284968951</v>
       </c>
       <c r="Y49" s="155" t="n">
         <v>0.024552655586236</v>
@@ -5763,7 +5763,7 @@
         <v>1483.644525484691</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>1639.702627229064</v>
+        <v>1639.702627229063</v>
       </c>
       <c r="AG49" s="159" t="n">
         <v>1821.392186934197</v>
@@ -6340,10 +6340,10 @@
         <v>0.009529046918664087</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.008814070349602295</v>
+        <v>0.008814070349602294</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0003206394028269367</v>
+        <v>0.0003206394028269369</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
@@ -6355,10 +6355,10 @@
         <v>0.0008684519473910424</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008478096656780366</v>
+        <v>0.0008478096656780364</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.289569736199423e-05</v>
+        <v>3.289569736199425e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0.009689845559503415</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008962804062908112</v>
+        <v>0.008962804062908111</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003260500572831679</v>
+        <v>0.000326050057283168</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0.001030192616305478</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>3.991714580723756e-05</v>
+        <v>3.991714580723759e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6420,10 +6420,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6544,10 +6544,10 @@
         <v>0.008214445044247924</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.007627179541740437</v>
+        <v>0.007627179541740435</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002778790844920279</v>
+        <v>0.0002778790844920281</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0.0007121161261154015</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006962503363034965</v>
+        <v>0.0006962503363034963</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.705516494001638e-05</v>
+        <v>2.705516494001639e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
@@ -6574,10 +6574,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6594,10 +6594,10 @@
         <v>0.008351753781564407</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.00775470083252093</v>
+        <v>0.007754700832520929</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002825254512606018</v>
+        <v>0.000282525451260602</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
@@ -6609,10 +6609,10 @@
         <v>0.0008345108556951456</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0008154269196345158</v>
+        <v>0.0008154269196345157</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.165965023269066e-05</v>
+        <v>3.165965023269068e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
@@ -6624,10 +6624,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6748,10 +6748,10 @@
         <v>0.007782301607069054</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.007229775608787415</v>
+        <v>0.007229775608787414</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002635306532242528</v>
+        <v>0.000263530653224253</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
@@ -6763,10 +6763,10 @@
         <v>0.0006825875452040658</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006673780591924067</v>
+        <v>0.0006673780591924064</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.593271830511209e-05</v>
+        <v>2.59327183051121e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
@@ -6778,10 +6778,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6798,10 +6798,10 @@
         <v>0.008008330891146932</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007438919682031655</v>
+        <v>0.007438919682031654</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002711252409240851</v>
+        <v>0.0002711252409240852</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
@@ -6813,10 +6813,10 @@
         <v>0.0007992860995885483</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007810476881747795</v>
+        <v>0.0007810476881747794</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>3.032648315699317e-05</v>
+        <v>3.032648315699319e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6828,10 +6828,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6952,10 +6952,10 @@
         <v>0.007782301607069054</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.007229775608787415</v>
+        <v>0.007229775608787414</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002635306532242528</v>
+        <v>0.000263530653224253</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0.0006825875452040658</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006673780591924067</v>
+        <v>0.0006673780591924064</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.593271830511209e-05</v>
+        <v>2.59327183051121e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
@@ -6982,10 +6982,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -7002,10 +7002,10 @@
         <v>0.008008330891146932</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.007438919682031655</v>
+        <v>0.007438919682031654</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002711252409240851</v>
+        <v>0.0002711252409240852</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
@@ -7017,10 +7017,10 @@
         <v>0.0007992860995885483</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007810476881747795</v>
+        <v>0.0007810476881747794</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>3.032648315699317e-05</v>
+        <v>3.032648315699319e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7032,10 +7032,10 @@
         <v>1055.184431768953</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1044.25254427548</v>
+        <v>1044.252544275479</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>41.02602937192312</v>
+        <v>41.02602937192314</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.004389790632988983</v>
+        <v>0.004389790632988982</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.006387224154446727</v>
+        <v>0.006387224154446728</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.008442347676483801</v>
+        <v>0.008442347676483794</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.01031668646141136</v>
@@ -7312,28 +7312,28 @@
         <v>0.01204674054031116</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003783626582433422</v>
+        <v>0.0003783626582433421</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005821145915954854</v>
+        <v>0.0005821145915954855</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0008120543264622842</v>
+        <v>0.0008120543264622835</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001058430725048308</v>
+        <v>0.001058430725048309</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.001331747090182217</v>
+        <v>0.001331747090182216</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>452.6917059904299</v>
+        <v>452.6917059904298</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>707.2794947404524</v>
+        <v>707.2794947404525</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>1000.212466108145</v>
+        <v>1000.212466108144</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1320.027039893261</v>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004463866495284433</v>
+        <v>0.004463866495284432</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006495005863524002</v>
+        <v>0.006495005863524004</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008584808726729313</v>
+        <v>0.008584808726729306</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.01049077618676587</v>
@@ -7362,13 +7362,13 @@
         <v>0.01225002419731908</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004607505280019642</v>
+        <v>0.000460750528001964</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0007081120416990315</v>
+        <v>0.0007081120416990316</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009867454984619855</v>
+        <v>0.0009867454984619848</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.001284348318069893</v>
@@ -7377,13 +7377,13 @@
         <v>0.001613238755209897</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>452.6917059904299</v>
+        <v>452.6917059904298</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>707.2794947404524</v>
+        <v>707.2794947404525</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>1000.212466108145</v>
+        <v>1000.212466108144</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1320.027039893261</v>
@@ -7501,16 +7501,16 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003758418674650036</v>
+        <v>0.003758418674650035</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.005506059761257968</v>
+        <v>0.005506059761257969</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.007305512541687689</v>
+        <v>0.007305512541687684</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.008940858059281074</v>
+        <v>0.008940858059281076</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.01045202489141601</v>
@@ -7519,25 +7519,25 @@
         <v>0.0003097098949182233</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004773242655135323</v>
+        <v>0.0004773242655135324</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006668868270614737</v>
+        <v>0.0006668868270614731</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008705095237423814</v>
+        <v>0.0008705095237423815</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.001097089532127489</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>452.6917059904299</v>
+        <v>452.6917059904298</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>707.2794947404524</v>
+        <v>707.2794947404525</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>1000.212466108145</v>
+        <v>1000.212466108144</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1320.027039893261</v>
@@ -7551,43 +7551,43 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003821217173064798</v>
+        <v>0.003821217173064797</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005598096424639972</v>
+        <v>0.005598096424639973</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007427655777471085</v>
+        <v>0.007427655777471079</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.00909035655732428</v>
+        <v>0.009090356557324281</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01062680317529137</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.0003631402539260209</v>
+        <v>0.0003631402539260208</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005593642197525566</v>
+        <v>0.0005593642197525567</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007810372832603294</v>
+        <v>0.0007810372832603288</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.001018660470450388</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.001282420571260687</v>
+        <v>0.001282420571260686</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>452.6917059904299</v>
+        <v>452.6917059904298</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>707.2794947404524</v>
+        <v>707.2794947404525</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>1000.212466108145</v>
+        <v>1000.212466108144</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1320.027039893261</v>
@@ -7612,13 +7612,13 @@
         <v>0.02293026875728913</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02891214347838031</v>
+        <v>0.0289121434783803</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03493993914006312</v>
+        <v>0.03493993914006311</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001202013507296027</v>
+        <v>0.001202013507296028</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.001876713097151192</v>
@@ -7627,13 +7627,13 @@
         <v>0.002659554063444628</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003541035171483905</v>
+        <v>0.003541035171483903</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004539058695875703</v>
+        <v>0.004539058695875702</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>76.05946338317244</v>
+        <v>76.05946338317248</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>120.2983458350366</v>
@@ -7642,10 +7642,10 @@
         <v>172.5671234889624</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>232.4112790863193</v>
+        <v>232.4112790863192</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>302.1614577989876</v>
+        <v>302.1614577989875</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01477718426049838</v>
+        <v>0.01477718426049839</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.02220351503836899</v>
@@ -7662,10 +7662,10 @@
         <v>0.03018847902881347</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.03806382063436034</v>
+        <v>0.03806382063436033</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.045999618720671</v>
+        <v>0.04599961872067099</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.00138188126588554</v>
@@ -7677,13 +7677,13 @@
         <v>0.003061392048896288</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.004079822765263514</v>
+        <v>0.004079822765263513</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>0.005235238901162374</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>76.05946338317244</v>
+        <v>76.05946338317248</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>120.2983458350366</v>
@@ -7692,10 +7692,10 @@
         <v>172.5671234889624</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>232.4112790863193</v>
+        <v>232.4112790863192</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>302.1614577989876</v>
+        <v>302.1614577989875</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,13 +7705,13 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.004156074374709218</v>
+        <v>0.004156074374709216</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.006103634743632753</v>
+        <v>0.006103634743632754</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.008119619452050954</v>
+        <v>0.008119619452050949</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.009972085784422385</v>
@@ -7720,13 +7720,13 @@
         <v>0.01169742855839976</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003467356301251904</v>
+        <v>0.0003467356301251903</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005353512709779973</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007495192333084779</v>
+        <v>0.0007495192333084774</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.0009813025103450812</v>
@@ -7735,19 +7735,19 @@
         <v>0.001239921512797902</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>528.7511693736024</v>
+        <v>528.7511693736022</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>827.5778405754889</v>
+        <v>827.5778405754891</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1172.779589597108</v>
+        <v>1172.779589597107</v>
       </c>
       <c r="P72" s="165" t="n">
         <v>1552.43831897958</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.0650206286</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,13 +7755,13 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004277402209740632</v>
+        <v>0.004277402209740631</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006280908802263816</v>
+        <v>0.006280908802263817</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008354505066388841</v>
+        <v>0.008354505066388834</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.010259467457535</v>
@@ -7770,13 +7770,13 @@
         <v>0.01203238892621377</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0004062181296861683</v>
+        <v>0.0004062181296861682</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006268775811926822</v>
+        <v>0.0006268775811926823</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008771793683576056</v>
+        <v>0.0008771793683576049</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001147564003964397</v>
@@ -7785,19 +7785,19 @@
         <v>0.001448570462989258</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>528.7511693736024</v>
+        <v>528.7511693736022</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>827.5778405754889</v>
+        <v>827.5778405754891</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1172.779589597108</v>
+        <v>1172.779589597107</v>
       </c>
       <c r="AG72" s="165" t="n">
         <v>1552.43831897958</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.0650206286</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.004156074374709218</v>
+        <v>0.004156074374709216</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.006103634743632753</v>
+        <v>0.006103634743632754</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.008119619452050954</v>
+        <v>0.008119619452050949</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>0.009972085784422385</v>
@@ -7924,13 +7924,13 @@
         <v>0.01169742855839976</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003467356301251904</v>
+        <v>0.0003467356301251903</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.0005353512709779973</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007495192333084779</v>
+        <v>0.0007495192333084774</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.0009813025103450812</v>
@@ -7939,19 +7939,19 @@
         <v>0.001239921512797902</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>528.7511693736024</v>
+        <v>528.7511693736022</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>827.5778405754889</v>
+        <v>827.5778405754891</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1172.779589597108</v>
+        <v>1172.779589597107</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>1552.43831897958</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.0650206286</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,13 +7959,13 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.004277402209740632</v>
+        <v>0.004277402209740631</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.006280908802263816</v>
+        <v>0.006280908802263817</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.008354505066388841</v>
+        <v>0.008354505066388834</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>0.010259467457535</v>
@@ -7974,13 +7974,13 @@
         <v>0.01203238892621377</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0004062181296861683</v>
+        <v>0.0004062181296861682</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006268775811926822</v>
+        <v>0.0006268775811926823</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008771793683576056</v>
+        <v>0.0008771793683576049</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.001147564003964397</v>
@@ -7989,19 +7989,19 @@
         <v>0.001448570462989258</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>528.7511693736024</v>
+        <v>528.7511693736022</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>827.5778405754889</v>
+        <v>827.5778405754891</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1172.779589597108</v>
+        <v>1172.779589597107</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>1552.43831897958</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.0650206286</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8269,7 +8269,7 @@
         <v>638.295663187813</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>683.8594162227297</v>
+        <v>683.8594162227295</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>730.1040237956695</v>
@@ -8284,7 +8284,7 @@
         <v>61.39651844682839</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>70.15991233727149</v>
+        <v>70.15991233727148</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>80.71178307249376</v>
@@ -8299,7 +8299,7 @@
         <v>75622481.31068681</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>87500276.78713894</v>
+        <v>87500276.78713891</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>102236374.632282</v>
@@ -8319,7 +8319,7 @@
         <v>649.066632831504</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>695.3992549487214</v>
+        <v>695.3992549487211</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>742.4242207366378</v>
@@ -8334,7 +8334,7 @@
         <v>74.60429213224558</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>85.13525096523726</v>
+        <v>85.13525096523723</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>97.77184978630247</v>
@@ -8349,7 +8349,7 @@
         <v>75622481.31068681</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>87500276.78713894</v>
+        <v>87500276.78713891</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>102236374.632282</v>
@@ -8365,7 +8365,7 @@
         <v>1607.554453379703</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1764.932686261068</v>
+        <v>1764.932686261069</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1914.694122473068</v>
@@ -8380,7 +8380,7 @@
         <v>105.0043627503358</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>117.2553896390425</v>
+        <v>117.2553896390426</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>131.6590735899129</v>
@@ -8395,7 +8395,7 @@
         <v>27848676.16132196</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>31276854.84995834</v>
+        <v>31276854.84995835</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>35300042.6721456</v>
@@ -8430,7 +8430,7 @@
         <v>105.4500329216494</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>117.7546469581878</v>
+        <v>117.7546469581879</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>132.2233787676779</v>
@@ -8445,7 +8445,7 @@
         <v>27848676.16132196</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>31276854.84995834</v>
+        <v>31276854.84995835</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>35300042.6721456</v>
@@ -8467,13 +8467,13 @@
         <v>694.1992632514564</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>753.0874257612755</v>
+        <v>753.0874257612757</v>
       </c>
       <c r="E81" s="162" t="n">
         <v>810.1737556474518</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>865.4550835011599</v>
+        <v>865.4550835011598</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>921.1319910551514</v>
@@ -8482,13 +8482,13 @@
         <v>57.20501079990412</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>65.28568848785076</v>
+        <v>65.28568848785078</v>
       </c>
       <c r="J81" s="162" t="n">
         <v>73.95705670055428</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>84.26337691123091</v>
+        <v>84.26337691123089</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>96.68597956787396</v>
@@ -8497,13 +8497,13 @@
         <v>83614486.83145005</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>96737652.16564414</v>
+        <v>96737652.16564415</v>
       </c>
       <c r="O81" s="165" t="n">
         <v>110922523.9828324</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>127775668.1137238</v>
+        <v>127775668.1137237</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>148666010.049729</v>
@@ -8517,13 +8517,13 @@
         <v>705.7984689564687</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>765.675675236827</v>
+        <v>765.6756752368271</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>823.7193136759794</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>879.9262040859425</v>
+        <v>879.9262040859423</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>936.535118228292</v>
@@ -8532,13 +8532,13 @@
         <v>67.07387296490164</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>76.50664514766807</v>
+        <v>76.50664514766808</v>
       </c>
       <c r="AA81" s="162" t="n">
         <v>86.61622377196309</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>98.60405753761182</v>
+        <v>98.60405753761179</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>113.0191160514357</v>
@@ -8547,13 +8547,13 @@
         <v>83614486.83145005</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>96737652.16564414</v>
+        <v>96737652.16564415</v>
       </c>
       <c r="AF81" s="165" t="n">
         <v>110922523.9828324</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>127775668.1137238</v>
+        <v>127775668.1137237</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>148666010.049729</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1566.878334560186</v>
+        <v>1566.878334560187</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>1724.455918176737</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>740.6807688387952</v>
+        <v>740.6807688387951</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>804.1889325360536</v>
@@ -8677,13 +8677,13 @@
         <v>866.1692853372944</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>926.4620427672997</v>
+        <v>926.4620427672995</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>987.2904828517676</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>61.79398873796593</v>
+        <v>61.79398873796591</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>70.53560463930657</v>
@@ -8692,13 +8692,13 @@
         <v>79.9557839496253</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>91.1684423861626</v>
+        <v>91.16844238616258</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>104.652291993652</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>94232149.70339718</v>
+        <v>94232149.70339717</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>109038133.531363</v>
@@ -8707,7 +8707,7 @@
         <v>125107545.369371</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>144230124.7065901</v>
+        <v>144230124.70659</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>167881766.0510357</v>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>762.303383361641</v>
+        <v>762.3033833616408</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>827.5458079004529</v>
@@ -8727,13 +8727,13 @@
         <v>891.2259651371916</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>953.1613931019818</v>
+        <v>953.1613931019817</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>1015.561925726948</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>72.39474790035722</v>
+        <v>72.3947479003572</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>82.59472167400372</v>
@@ -8748,7 +8748,7 @@
         <v>122.2627541351808</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>94232149.70339718</v>
+        <v>94232149.70339717</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>109038133.531363</v>
@@ -8757,7 +8757,7 @@
         <v>125107545.369371</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>144230124.7065901</v>
+        <v>144230124.70659</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>167881766.0510357</v>
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>740.6807688387952</v>
+        <v>740.6807688387951</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>804.1889325360536</v>
@@ -8881,13 +8881,13 @@
         <v>866.1692853372944</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>926.4620427672997</v>
+        <v>926.4620427672995</v>
       </c>
       <c r="G85" s="181" t="n">
         <v>987.2904828517676</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>61.79398873796593</v>
+        <v>61.79398873796591</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>70.53560463930657</v>
@@ -8896,13 +8896,13 @@
         <v>79.9557839496253</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>91.1684423861626</v>
+        <v>91.16844238616258</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>104.652291993652</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>94232149.70339718</v>
+        <v>94232149.70339717</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>109038133.531363</v>
@@ -8911,7 +8911,7 @@
         <v>125107545.369371</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>144230124.7065901</v>
+        <v>144230124.70659</v>
       </c>
       <c r="Q85" s="184" t="n">
         <v>167881766.0510357</v>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>762.303383361641</v>
+        <v>762.3033833616408</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>827.5458079004529</v>
@@ -8931,13 +8931,13 @@
         <v>891.2259651371916</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>953.1613931019818</v>
+        <v>953.1613931019817</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1015.561925726948</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>72.39474790035722</v>
+        <v>72.3947479003572</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>82.59472167400372</v>
@@ -8952,7 +8952,7 @@
         <v>122.2627541351808</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>94232149.70339718</v>
+        <v>94232149.70339717</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>109038133.531363</v>
@@ -8961,7 +8961,7 @@
         <v>125107545.369371</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>144230124.7065901</v>
+        <v>144230124.70659</v>
       </c>
       <c r="AH85" s="190" t="n">
         <v>167881766.0510357</v>
